--- a/data/profiles/mandatory_1815.xlsx
+++ b/data/profiles/mandatory_1815.xlsx
@@ -12934,8 +12934,10 @@
       <c r="B4" t="s">
         <v>111</v>
       </c>
-      <c r="C4" t="s">
-        <v>112</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No Change</t>
+        </is>
       </c>
       <c r="D4" t="s">
         <v>113</v>
@@ -13949,8 +13951,10 @@
       <c r="B42" t="s">
         <v>315</v>
       </c>
-      <c r="C42" t="s">
-        <v>316</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disable</t>
+        </is>
       </c>
       <c r="D42" t="s">
         <v>145</v>
@@ -14157,8 +14161,10 @@
       <c r="B50" t="s">
         <v>352</v>
       </c>
-      <c r="C50" t="s">
-        <v>316</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Submitted</t>
+        </is>
       </c>
       <c r="D50" t="s">
         <v>353</v>
@@ -14417,8 +14423,10 @@
       <c r="B60" t="s">
         <v>389</v>
       </c>
-      <c r="C60" t="s">
-        <v>390</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disable</t>
+        </is>
       </c>
       <c r="D60" t="s">
         <v>145</v>
@@ -14647,11 +14655,15 @@
       <c r="C8">
         <v>3</v>
       </c>
-      <c r="D8" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" t="s">
-        <v>139</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Ready</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ready</t>
+        </is>
       </c>
       <c r="F8" t="s">
         <v>140</v>
@@ -14676,8 +14688,10 @@
       <c r="C9">
         <v>3</v>
       </c>
-      <c r="D9" t="s">
-        <v>422</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amp-hrs (default)</t>
+        </is>
       </c>
       <c r="E9" t="s">
         <v>423</v>
@@ -15339,8 +15353,11 @@
       <c r="D33" t="s">
         <v>505</v>
       </c>
-      <c r="E33" t="s">
-        <v>506</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked
+(Disabled)</t>
+        </is>
       </c>
       <c r="F33" t="s">
         <v>507</v>
@@ -15365,8 +15382,11 @@
       <c r="D34" t="s">
         <v>511</v>
       </c>
-      <c r="E34" t="s">
-        <v>512</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Started
+(Evaluating)</t>
+        </is>
       </c>
       <c r="F34" t="s">
         <v>513</v>
@@ -15417,8 +15437,11 @@
       <c r="D36" t="s">
         <v>505</v>
       </c>
-      <c r="E36" t="s">
-        <v>506</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked
+(Disabled)</t>
+        </is>
       </c>
       <c r="F36" t="s">
         <v>521</v>
@@ -15443,8 +15466,11 @@
       <c r="D37" t="s">
         <v>511</v>
       </c>
-      <c r="E37" t="s">
-        <v>512</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Started
+(Evaluating)</t>
+        </is>
       </c>
       <c r="F37" t="s">
         <v>524</v>
@@ -15495,8 +15521,11 @@
       <c r="D39" t="s">
         <v>505</v>
       </c>
-      <c r="E39" t="s">
-        <v>506</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked
+(Disabled)</t>
+        </is>
       </c>
       <c r="F39" t="s">
         <v>530</v>
@@ -15521,8 +15550,11 @@
       <c r="D40" t="s">
         <v>511</v>
       </c>
-      <c r="E40" t="s">
-        <v>512</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Started
+(Evaluating)</t>
+        </is>
       </c>
       <c r="F40" t="s">
         <v>533</v>
@@ -15573,8 +15605,11 @@
       <c r="D42" t="s">
         <v>505</v>
       </c>
-      <c r="E42" t="s">
-        <v>506</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocked
+(Disabled)</t>
+        </is>
       </c>
       <c r="F42" t="s">
         <v>539</v>
@@ -15599,8 +15634,11 @@
       <c r="D43" t="s">
         <v>511</v>
       </c>
-      <c r="E43" t="s">
-        <v>512</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Started
+(Evaluating)</t>
+        </is>
       </c>
       <c r="F43" t="s">
         <v>542</v>
@@ -16732,11 +16770,15 @@
       <c r="C83">
         <v>1</v>
       </c>
-      <c r="D83" t="s">
-        <v>612</v>
-      </c>
-      <c r="E83" t="s">
-        <v>613</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normal: No Active Communications Error </t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alarm: Active Communications Error </t>
+        </is>
       </c>
       <c r="F83" t="s">
         <v>614</v>
@@ -17170,8 +17212,10 @@
       <c r="D98" t="s">
         <v>316</v>
       </c>
-      <c r="E98" t="s">
-        <v>353</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validated</t>
+        </is>
       </c>
       <c r="F98" t="s">
         <v>354</v>
@@ -17704,11 +17748,15 @@
       <c r="C119">
         <v>1</v>
       </c>
-      <c r="D119" t="s">
-        <v>612</v>
-      </c>
-      <c r="E119" t="s">
-        <v>613</v>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normal: No Active Communications Error </t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alarm: Active Communications Error </t>
+        </is>
       </c>
       <c r="F119" t="s">
         <v>674</v>
@@ -20792,6 +20840,11 @@
       <c r="H24" t="s">
         <v>1065</v>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI101</t>
+        </is>
+      </c>
       <c r="J24" t="s">
         <v>159</v>
       </c>
@@ -20912,7 +20965,7 @@
         <v>1080</v>
       </c>
       <c r="C28">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>1000</v>
@@ -24556,10 +24609,10 @@
         <v>1508</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E131">
         <v>1</v>
@@ -24597,7 +24650,7 @@
         <v>0</v>
       </c>
       <c r="D132">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -24673,7 +24726,7 @@
         <v>0</v>
       </c>
       <c r="D134">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -24711,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="D135">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -26173,7 +26226,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E176">
         <v>1</v>
@@ -26208,7 +26261,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E177">
         <v>1</v>
@@ -26243,7 +26296,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E178">
         <v>1</v>
@@ -26278,7 +26331,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E179">
         <v>1</v>
@@ -26313,7 +26366,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E180">
         <v>1</v>
@@ -26348,7 +26401,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -26383,7 +26436,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E182">
         <v>1</v>
@@ -26418,10 +26471,10 @@
         <v>0</v>
       </c>
       <c r="D183">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E183">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -26456,10 +26509,10 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E184">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -26494,10 +26547,10 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E185">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -26532,10 +26585,10 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E186">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="F186">
         <v>0</v>
@@ -26567,13 +26620,13 @@
         <v>1732</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D187">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E187">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F187">
         <v>0</v>
@@ -26602,10 +26655,10 @@
         <v>1737</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D188">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E188">
         <v>1</v>
@@ -26637,13 +26690,13 @@
         <v>1742</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D189">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E189">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -26672,10 +26725,10 @@
         <v>1746</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D190">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E190">
         <v>1</v>
@@ -26707,13 +26760,13 @@
         <v>1750</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D191">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -26742,10 +26795,10 @@
         <v>1754</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D192">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E192">
         <v>1</v>
@@ -26777,13 +26830,13 @@
         <v>1758</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D193">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E193">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -26812,10 +26865,10 @@
         <v>1762</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D194">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -26847,10 +26900,10 @@
         <v>1766</v>
       </c>
       <c r="C195">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D195">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -26882,10 +26935,10 @@
         <v>1771</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D196">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -26917,10 +26970,10 @@
         <v>1775</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D197">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -26952,10 +27005,10 @@
         <v>1779</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D198">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E198">
         <v>1</v>
@@ -26987,10 +27040,10 @@
         <v>1783</v>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D199">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -27022,10 +27075,10 @@
         <v>1787</v>
       </c>
       <c r="C200">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D200">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -27057,10 +27110,10 @@
         <v>1791</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D201">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -27092,10 +27145,10 @@
         <v>1795</v>
       </c>
       <c r="C202">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D202">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E202">
         <v>1</v>
@@ -27127,13 +27180,13 @@
         <v>1799</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D203">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E203">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -27162,10 +27215,10 @@
         <v>1803</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D204">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E204">
         <v>1</v>
@@ -27197,13 +27250,13 @@
         <v>1807</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D205">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E205">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -27232,10 +27285,10 @@
         <v>1811</v>
       </c>
       <c r="C206">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D206">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E206">
         <v>1</v>
@@ -27267,10 +27320,10 @@
         <v>1815</v>
       </c>
       <c r="C207">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D207">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E207">
         <v>1</v>
@@ -27302,10 +27355,10 @@
         <v>1125</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D208">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E208">
         <v>1</v>
@@ -27340,10 +27393,10 @@
         <v>1131</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D209">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E209">
         <v>1</v>
@@ -27378,10 +27431,10 @@
         <v>1827</v>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="D210">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="E210">
         <v>1</v>
@@ -27699,7 +27752,7 @@
         <v>0</v>
       </c>
       <c r="D219">
-        <v>2147483647</v>
+        <v>100</v>
       </c>
       <c r="E219">
         <v>1</v>
@@ -29449,7 +29502,7 @@
         <v>0</v>
       </c>
       <c r="D269">
-        <v>2147483647</v>
+        <v>100</v>
       </c>
       <c r="E269">
         <v>1</v>
@@ -36981,8 +37034,10 @@
       <c r="J87">
         <v>0</v>
       </c>
-      <c r="K87" t="s">
-        <v>1059</v>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AO47</t>
+        </is>
       </c>
       <c r="L87" t="s">
         <v>159</v>
@@ -37321,7 +37376,7 @@
         <v>-1000</v>
       </c>
       <c r="E96">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F96">
         <v>0.1</v>
@@ -43505,10 +43560,10 @@
         <v>2</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E248">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F248">
         <v>1</v>
@@ -43523,7 +43578,7 @@
         <v>1509</v>
       </c>
       <c r="J248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K248" t="s">
         <v>1507</v>
@@ -43552,7 +43607,7 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F249">
         <v>1</v>
@@ -43640,7 +43695,7 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="F251">
         <v>1</v>
@@ -43684,7 +43739,7 @@
         <v>0</v>
       </c>
       <c r="E252">
-        <v>100</v>
+        <v>255</v>
       </c>
       <c r="F252">
         <v>1</v>
@@ -44572,7 +44627,7 @@
         <v>0</v>
       </c>
       <c r="E273">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F273">
         <v>1</v>
@@ -44610,7 +44665,7 @@
         <v>0</v>
       </c>
       <c r="E274">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F274">
         <v>1</v>
@@ -44648,7 +44703,7 @@
         <v>0</v>
       </c>
       <c r="E275">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F275">
         <v>1</v>
@@ -44686,10 +44741,10 @@
         <v>0</v>
       </c>
       <c r="E276">
-        <v>100</v>
+        <v>70000</v>
       </c>
       <c r="F276">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G276">
         <v>0</v>
@@ -44724,10 +44779,10 @@
         <v>3</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E277">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F277">
         <v>1</v>
@@ -44765,10 +44820,10 @@
         <v>1</v>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E278">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F278">
         <v>1</v>
@@ -44803,10 +44858,10 @@
         <v>1</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E279">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F279">
         <v>1</v>
@@ -44841,10 +44896,10 @@
         <v>1</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E280">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F280">
         <v>1</v>
@@ -44879,10 +44934,10 @@
         <v>3</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E281">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F281">
         <v>1</v>
@@ -44920,10 +44975,10 @@
         <v>1</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E282">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F282">
         <v>1</v>
@@ -44958,10 +45013,10 @@
         <v>1</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E283">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F283">
         <v>1</v>
@@ -44996,10 +45051,10 @@
         <v>1</v>
       </c>
       <c r="D284">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E284">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -45034,13 +45089,13 @@
         <v>3</v>
       </c>
       <c r="D285">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E285">
         <v>100</v>
       </c>
       <c r="F285">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="G285">
         <v>0</v>
@@ -45072,10 +45127,10 @@
         <v>3</v>
       </c>
       <c r="D286">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E286">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F286">
         <v>1</v>
@@ -45113,10 +45168,10 @@
         <v>0</v>
       </c>
       <c r="E287">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F287">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G287">
         <v>0</v>
@@ -45154,10 +45209,10 @@
         <v>0</v>
       </c>
       <c r="E288">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="F288">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G288">
         <v>0</v>
@@ -45195,10 +45250,10 @@
         <v>0</v>
       </c>
       <c r="E289">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F289">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G289">
         <v>0</v>
@@ -45236,10 +45291,10 @@
         <v>0</v>
       </c>
       <c r="E290">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="F290">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G290">
         <v>0</v>
@@ -45277,10 +45332,10 @@
         <v>0</v>
       </c>
       <c r="E291">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F291">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G291">
         <v>0</v>
@@ -45318,10 +45373,10 @@
         <v>0</v>
       </c>
       <c r="E292">
-        <v>100</v>
+        <v>3600</v>
       </c>
       <c r="F292">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G292">
         <v>0</v>
@@ -45359,10 +45414,10 @@
         <v>0</v>
       </c>
       <c r="E293">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F293">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G293">
         <v>0</v>
@@ -45397,13 +45452,13 @@
         <v>1</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E294">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F294">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G294">
         <v>0</v>
@@ -45438,13 +45493,13 @@
         <v>1</v>
       </c>
       <c r="D295">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E295">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F295">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -45479,13 +45534,13 @@
         <v>1</v>
       </c>
       <c r="D296">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E296">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F296">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G296">
         <v>0</v>
@@ -45523,7 +45578,7 @@
         <v>0</v>
       </c>
       <c r="E297">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F297">
         <v>1</v>
@@ -45564,7 +45619,7 @@
         <v>0</v>
       </c>
       <c r="E298">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F298">
         <v>1</v>
@@ -45605,7 +45660,7 @@
         <v>0</v>
       </c>
       <c r="E299">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F299">
         <v>1</v>
@@ -45646,7 +45701,7 @@
         <v>0</v>
       </c>
       <c r="E300">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F300">
         <v>1</v>
@@ -45684,13 +45739,13 @@
         <v>3</v>
       </c>
       <c r="D301">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E301">
         <v>100</v>
       </c>
       <c r="F301">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="G301">
         <v>0</v>
@@ -45725,13 +45780,13 @@
         <v>3</v>
       </c>
       <c r="D302">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E302">
         <v>100</v>
       </c>
       <c r="F302">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -45769,10 +45824,10 @@
         <v>0</v>
       </c>
       <c r="E303">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F303">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G303">
         <v>0</v>
@@ -45810,10 +45865,10 @@
         <v>0</v>
       </c>
       <c r="E304">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F304">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G304">
         <v>0</v>
@@ -45851,10 +45906,10 @@
         <v>0</v>
       </c>
       <c r="E305">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F305">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G305">
         <v>0</v>
@@ -45892,10 +45947,10 @@
         <v>0</v>
       </c>
       <c r="E306">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F306">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G306">
         <v>0</v>
@@ -45933,10 +45988,10 @@
         <v>0</v>
       </c>
       <c r="E307">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F307">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -45974,10 +46029,10 @@
         <v>0</v>
       </c>
       <c r="E308">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F308">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G308">
         <v>0</v>
@@ -46015,10 +46070,10 @@
         <v>0</v>
       </c>
       <c r="E309">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F309">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G309">
         <v>0</v>
@@ -46059,10 +46114,10 @@
         <v>0</v>
       </c>
       <c r="E310">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F310">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G310">
         <v>0</v>
@@ -46103,10 +46158,10 @@
         <v>0</v>
       </c>
       <c r="E311">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F311">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G311">
         <v>0</v>
@@ -46147,10 +46202,10 @@
         <v>0</v>
       </c>
       <c r="E312">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F312">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="G312">
         <v>0</v>
@@ -46188,10 +46243,10 @@
         <v>2</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E313">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F313">
         <v>1</v>
@@ -46229,10 +46284,10 @@
         <v>2</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E314">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F314">
         <v>1</v>
@@ -46273,10 +46328,10 @@
         <v>2</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E315">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F315">
         <v>1</v>
@@ -46317,10 +46372,10 @@
         <v>2</v>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="E316">
-        <v>100</v>
+        <v>2147483647</v>
       </c>
       <c r="F316">
         <v>1</v>
@@ -46481,7 +46536,7 @@
         <v>3</v>
       </c>
       <c r="D320">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E320">
         <v>2147483647</v>
@@ -46499,7 +46554,7 @@
         <v>1842</v>
       </c>
       <c r="J320">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K320" t="s">
         <v>1840</v>
@@ -46525,7 +46580,7 @@
         <v>0</v>
       </c>
       <c r="E321">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="F321">
         <v>1</v>
@@ -50846,7 +50901,7 @@
         <v>3</v>
       </c>
       <c r="D431">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E431">
         <v>2147483647</v>
@@ -50864,7 +50919,7 @@
         <v>2038</v>
       </c>
       <c r="J431">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K431" t="s">
         <v>2037</v>
@@ -51391,7 +51446,7 @@
         <v>2077</v>
       </c>
       <c r="J444">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K444" t="s">
         <v>2076</v>
